--- a/HSI_FSC_result/4. C Way/score_30way.xlsx
+++ b/HSI_FSC_result/4. C Way/score_30way.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\DevelopProject\Develop_DeepLearning\HSI\HSI-FSC\HSI_FSC_4_30way\result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\DevelopProject\Develop_DeepLearning\HSI\HSI-FSC\HSI_FSC_result\4. C Way\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C58B40E-84BA-4975-A62F-9BB84138E066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3738553A-B137-4DDA-950E-39843CB00B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="1815" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="12885" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IP" sheetId="1" r:id="rId1"/>
@@ -39,12 +39,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -79,7 +86,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -358,9 +365,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>64.705889999999997</v>
       </c>
@@ -396,7 +403,7 @@
         <v>33.346591799999999</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>52.113819999999997</v>
       </c>
@@ -432,7 +439,7 @@
         <v>47.325700499999996</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>43.574764000000002</v>
       </c>
@@ -468,7 +475,7 @@
         <v>38.120671700000003</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>43.496803</v>
       </c>
@@ -504,7 +511,7 @@
         <v>46.677878199999995</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>50.793655000000001</v>
       </c>
@@ -540,7 +547,7 @@
         <v>61.039537900000006</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>92.028983999999994</v>
       </c>
@@ -576,7 +583,7 @@
         <v>88.463335700000002</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>15.135135</v>
       </c>
@@ -612,7 +619,7 @@
         <v>23.5691597</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>96.754559999999998</v>
       </c>
@@ -648,7 +655,7 @@
         <v>93.388533899999999</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>30.158731</v>
       </c>
@@ -684,7 +691,7 @@
         <v>24.616685799999999</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>37.131630000000001</v>
       </c>
@@ -720,7 +727,7 @@
         <v>42.802908299999999</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>69.822069999999997</v>
       </c>
@@ -756,7 +763,7 @@
         <v>68.0592288</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>37</v>
       </c>
@@ -792,7 +799,7 @@
         <v>36.631828599999999</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>64.668769999999995</v>
       </c>
@@ -828,7 +835,7 @@
         <v>67.050586799999991</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>96.195650000000001</v>
       </c>
@@ -864,7 +871,7 @@
         <v>92.748532499999996</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>91.304349999999999</v>
       </c>
@@ -900,7 +907,7 @@
         <v>70.396798899999993</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>92.783510000000007</v>
       </c>
@@ -936,7 +943,7 @@
         <v>73.264465000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>59.6350863498877</v>
       </c>
@@ -972,7 +979,7 @@
         <v>57.807590984486218</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>61.104267835617001</v>
       </c>
@@ -1008,7 +1015,7 @@
         <v>56.718901395797687</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>55.146858367918902</v>
       </c>
@@ -1045,6 +1052,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -1053,9 +1061,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C6D9CA-287C-4A13-BF9B-099121023619}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>94.043149999999997</v>
       </c>
@@ -1080,18 +1088,18 @@
       <c r="H1">
         <v>90.2834</v>
       </c>
-      <c r="I1">
+      <c r="I1" s="1">
         <v>99.698490000000007</v>
       </c>
       <c r="J1">
         <v>99.844399999999993</v>
       </c>
       <c r="K1" s="1">
-        <f>AVERAGE(A1:J1)</f>
+        <f t="shared" ref="K1:K19" si="0">AVERAGE(A1:J1)</f>
         <v>94.129437999999993</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>99.125690000000006</v>
       </c>
@@ -1116,18 +1124,18 @@
       <c r="H2">
         <v>97.706909999999993</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>96.276730000000001</v>
       </c>
       <c r="J2">
         <v>97.765816000000001</v>
       </c>
       <c r="K2" s="1">
-        <f>AVERAGE(A2:J2)</f>
+        <f t="shared" si="0"/>
         <v>94.942970099999997</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>95.979645000000005</v>
       </c>
@@ -1152,18 +1160,18 @@
       <c r="H3">
         <v>100</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>94.939269999999993</v>
       </c>
       <c r="J3">
         <v>92.904449999999997</v>
       </c>
       <c r="K3" s="1">
-        <f>AVERAGE(A3:J3)</f>
+        <f t="shared" si="0"/>
         <v>90.157529499999995</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>86.907730000000001</v>
       </c>
@@ -1188,18 +1196,18 @@
       <c r="H4">
         <v>94.636795000000006</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>96.071669999999997</v>
       </c>
       <c r="J4">
         <v>96.733840000000001</v>
       </c>
       <c r="K4" s="1">
-        <f>AVERAGE(A4:J4)</f>
+        <f t="shared" si="0"/>
         <v>92.605189899999999</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>99.147030000000001</v>
       </c>
@@ -1224,18 +1232,18 @@
       <c r="H5">
         <v>99.059089999999998</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>97.532269999999997</v>
       </c>
       <c r="J5">
         <v>97.683250000000001</v>
       </c>
       <c r="K5" s="1">
-        <f>AVERAGE(A5:J5)</f>
+        <f t="shared" si="0"/>
         <v>98.2595575</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>100</v>
       </c>
@@ -1260,18 +1268,18 @@
       <c r="H6">
         <v>100</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>89.796859999999995</v>
       </c>
       <c r="J6">
         <v>91.428569999999993</v>
       </c>
       <c r="K6" s="1">
-        <f>AVERAGE(A6:J6)</f>
+        <f t="shared" si="0"/>
         <v>97.88665300000001</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>97.341740000000001</v>
       </c>
@@ -1296,18 +1304,18 @@
       <c r="H7">
         <v>92.909090000000006</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>95.437690000000003</v>
       </c>
       <c r="J7">
         <v>99.828963999999999</v>
       </c>
       <c r="K7" s="1">
-        <f>AVERAGE(A7:J7)</f>
+        <f t="shared" si="0"/>
         <v>95.940133500000002</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>74.596180000000004</v>
       </c>
@@ -1332,18 +1340,18 @@
       <c r="H8">
         <v>90.873726000000005</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>85.977900000000005</v>
       </c>
       <c r="J8">
         <v>91.141729999999995</v>
       </c>
       <c r="K8" s="1">
-        <f>AVERAGE(A8:J8)</f>
+        <f t="shared" si="0"/>
         <v>84.038544599999994</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>97.913376</v>
       </c>
@@ -1368,18 +1376,18 @@
       <c r="H9">
         <v>98.101264999999998</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>98.777540000000002</v>
       </c>
       <c r="J9">
         <v>99.838189999999997</v>
       </c>
       <c r="K9" s="1">
-        <f>AVERAGE(A9:J9)</f>
+        <f t="shared" si="0"/>
         <v>98.253968600000007</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>96.923079999999999</v>
       </c>
@@ -1404,18 +1412,18 @@
       <c r="H10">
         <v>84.310400000000001</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>88.767430000000004</v>
       </c>
       <c r="J10">
         <v>98.484849999999994</v>
       </c>
       <c r="K10" s="1">
-        <f>AVERAGE(A10:J10)</f>
+        <f t="shared" si="0"/>
         <v>92.803861499999996</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>92.674319999999994</v>
       </c>
@@ -1440,18 +1448,18 @@
       <c r="H11">
         <v>86.900689999999997</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>92.537315000000007</v>
       </c>
       <c r="J11">
         <v>26.268429999999999</v>
       </c>
       <c r="K11" s="1">
-        <f>AVERAGE(A11:J11)</f>
+        <f t="shared" si="0"/>
         <v>88.418466600000002</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>98.995766000000003</v>
       </c>
@@ -1476,18 +1484,18 @@
       <c r="H12">
         <v>97.666160000000005</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>99.93947</v>
       </c>
       <c r="J12">
         <v>96.042079999999999</v>
       </c>
       <c r="K12" s="1">
-        <f>AVERAGE(A12:J12)</f>
+        <f t="shared" si="0"/>
         <v>97.654414199999991</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>96.424706</v>
       </c>
@@ -1512,18 +1520,18 @@
       <c r="H13">
         <v>73.180700000000002</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>94.502075000000005</v>
       </c>
       <c r="J13">
         <v>99.303939999999997</v>
       </c>
       <c r="K13" s="1">
-        <f>AVERAGE(A13:J13)</f>
+        <f t="shared" si="0"/>
         <v>90.176481100000004</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>99.617590000000007</v>
       </c>
@@ -1548,18 +1556,18 @@
       <c r="H14">
         <v>76.379689999999997</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>70.905460000000005</v>
       </c>
       <c r="J14">
         <v>76.034229999999994</v>
       </c>
       <c r="K14" s="1">
-        <f>AVERAGE(A14:J14)</f>
+        <f t="shared" si="0"/>
         <v>87.450365399999981</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>67.226240000000004</v>
       </c>
@@ -1584,18 +1592,18 @@
       <c r="H15">
         <v>56.397860000000001</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>69.179519999999997</v>
       </c>
       <c r="J15">
         <v>65.996346000000003</v>
       </c>
       <c r="K15" s="1">
-        <f>AVERAGE(A15:J15)</f>
+        <f t="shared" si="0"/>
         <v>61.162243099999998</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>100</v>
       </c>
@@ -1620,18 +1628,18 @@
       <c r="H16">
         <v>87.154470000000003</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>99.571870000000004</v>
       </c>
       <c r="J16">
         <v>83.060683999999995</v>
       </c>
       <c r="K16" s="1">
-        <f>AVERAGE(A16:J16)</f>
+        <f t="shared" si="0"/>
         <v>82.433829400000008</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>88.584677344861305</v>
       </c>
@@ -1656,18 +1664,18 @@
       <c r="H17">
         <v>85.122577546232094</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>88.941232980472506</v>
       </c>
       <c r="J17">
         <v>84.621921705555195</v>
       </c>
       <c r="K17" s="1">
-        <f>AVERAGE(A17:J17)</f>
+        <f t="shared" si="0"/>
         <v>85.937297936411113</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>93.557262420654297</v>
       </c>
@@ -1692,18 +1700,18 @@
       <c r="H18">
         <v>89.097511768340993</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>91.869473457336397</v>
       </c>
       <c r="J18">
         <v>88.272488117218003</v>
       </c>
       <c r="K18" s="1">
-        <f>AVERAGE(A18:J18)</f>
+        <f t="shared" si="0"/>
         <v>90.394602417945819</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>87.264116673741796</v>
       </c>
@@ -1728,18 +1736,19 @@
       <c r="H19">
         <v>83.588217316868395</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>87.706388521915699</v>
       </c>
       <c r="J19">
         <v>83.006334419340007</v>
       </c>
       <c r="K19" s="1">
-        <f>AVERAGE(A19:J19)</f>
+        <f t="shared" si="0"/>
         <v>84.423196011030356</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -1748,9 +1757,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF268C6-262B-4B5D-895F-55B8B1A5BC12}">
   <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>84.65719</v>
       </c>
@@ -1766,7 +1775,7 @@
       <c r="E1">
         <v>95.459919999999997</v>
       </c>
-      <c r="F1">
+      <c r="F1" s="1">
         <v>85.425704999999994</v>
       </c>
       <c r="G1">
@@ -1786,7 +1795,7 @@
         <v>88.840453599999989</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>93.003555000000006</v>
       </c>
@@ -1802,7 +1811,7 @@
       <c r="E2">
         <v>94.49503</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>89.072789999999998</v>
       </c>
       <c r="G2">
@@ -1822,7 +1831,7 @@
         <v>92.563658500000003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>57.542453999999999</v>
       </c>
@@ -1838,7 +1847,7 @@
       <c r="E3">
         <v>31.083876</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>86.415880000000001</v>
       </c>
       <c r="G3">
@@ -1858,7 +1867,7 @@
         <v>51.713974499999992</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>82.418319999999994</v>
       </c>
@@ -1874,7 +1883,7 @@
       <c r="E4">
         <v>90.262180000000001</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>84.001260000000002</v>
       </c>
       <c r="G4">
@@ -1894,7 +1903,7 @@
         <v>82.242330199999998</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>98.593636000000004</v>
       </c>
@@ -1910,7 +1919,7 @@
       <c r="E5">
         <v>96.277739999999994</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>86.439589999999995</v>
       </c>
       <c r="G5">
@@ -1930,7 +1939,7 @@
         <v>91.793442199999987</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>40.823616000000001</v>
       </c>
@@ -1946,7 +1955,7 @@
       <c r="E6">
         <v>34.787745999999999</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>50.104934999999998</v>
       </c>
       <c r="G6">
@@ -1966,7 +1975,7 @@
         <v>37.915383199999994</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>56.622999999999998</v>
       </c>
@@ -1982,7 +1991,7 @@
       <c r="E7">
         <v>78.333336000000003</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>78.291820000000001</v>
       </c>
       <c r="G7">
@@ -2002,7 +2011,7 @@
         <v>66.935658300000014</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>70.970280000000002</v>
       </c>
@@ -2018,7 +2027,7 @@
       <c r="E8">
         <v>73.621870000000001</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>75.682159999999996</v>
       </c>
       <c r="G8">
@@ -2038,7 +2047,7 @@
         <v>72.616423400000002</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>87.262360000000001</v>
       </c>
@@ -2054,7 +2063,7 @@
       <c r="E9">
         <v>93.136219999999994</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>72.245766000000003</v>
       </c>
       <c r="G9">
@@ -2074,7 +2083,7 @@
         <v>70.241495700000002</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>75.4628763792781</v>
       </c>
@@ -2090,7 +2099,7 @@
       <c r="E10">
         <v>68.017112399476304</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>80.6036095006545</v>
       </c>
       <c r="G10">
@@ -2110,7 +2119,7 @@
         <v>71.861090331026702</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>74.654930830001803</v>
       </c>
@@ -2126,7 +2135,7 @@
       <c r="E11">
         <v>76.384210586547795</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>78.631103038787799</v>
       </c>
       <c r="G11">
@@ -2146,7 +2155,7 @@
         <v>72.762534618377629</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>68.727830700111696</v>
       </c>
@@ -2162,7 +2171,7 @@
       <c r="E12">
         <v>60.600945914660699</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>74.503633339844399</v>
       </c>
       <c r="G12">
@@ -2183,15 +2192,18 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B3FC5D-CBEF-4852-9492-3A8AFB021ED5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2199,8 +2211,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0042C639-A362-44FB-9C81-3BA17FB792FE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>